--- a/templates/joblink_tracker_template.xlsx
+++ b/templates/joblink_tracker_template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rd1532a91db1f43f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input" sheetId="2" r:id="R32ec1a17d8d14163"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="3" r:id="Rf5101fb869c84a35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="R8e6ba2dfec344b32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input" sheetId="2" r:id="R0e220bf9b6994a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="3" r:id="Ra9d996b4e37c4b9a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -281,7 +281,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -292,7 +292,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -303,7 +303,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -314,7 +314,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -325,7 +325,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -336,7 +336,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -600,7 +600,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="21" t="str">
-        <x:v>Paste one job link per row in the Input sheet.</x:v>
+        <x:v>Paste one job link on each row of the Input sheet.</x:v>
       </x:c>
       <x:c r="C4" s="22" t="str"/>
       <x:c r="D4" s="22" t="str"/>
@@ -612,7 +612,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="24" t="str">
-        <x:v>Run JobLink Beta or the Excel workflow to extract job details.</x:v>
+        <x:v>Run JobLink to fill in the job details.</x:v>
       </x:c>
       <x:c r="C5" s="25" t="str"/>
       <x:c r="D5" s="25" t="str"/>
@@ -624,7 +624,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
-        <x:v>Review rows marked Review or Error before using them for real applications.</x:v>
+        <x:v>Check every row marked Review or Error before saving it.</x:v>
       </x:c>
       <x:c r="C6" s="25" t="str"/>
       <x:c r="D6" s="25" t="str"/>
@@ -636,7 +636,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="24" t="str">
-        <x:v>Saved jobs belong in the Applications sheet.</x:v>
+        <x:v>Finished jobs appear on the Applications sheet.</x:v>
       </x:c>
       <x:c r="C7" s="25" t="str"/>
       <x:c r="D7" s="25" t="str"/>
@@ -648,7 +648,7 @@
         <x:v>Privacy</x:v>
       </x:c>
       <x:c r="B8" s="27" t="str">
-        <x:v>Do not commit personal tracker files, logs, or private application notes.</x:v>
+        <x:v>Keep personal trackers, logs, and private notes out of GitHub.</x:v>
       </x:c>
       <x:c r="C8" s="28" t="str"/>
       <x:c r="D8" s="28" t="str"/>
@@ -2308,7 +2308,7 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="42" t="str">
-        <x:v>Paste links in Job Link. Leave Process Status blank or Pending before running the workflow.</x:v>
+        <x:v>Paste one link in each Job Link row. Leave Process Status blank or set it to Pending.</x:v>
       </x:c>
       <x:c r="B205" s="42" t="str"/>
       <x:c r="C205" s="42" t="str"/>
@@ -2318,7 +2318,7 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="42" t="str">
-        <x:v>Use a copied tracker when testing. Keep private applications out of GitHub.</x:v>
+        <x:v>Test with a copy of your tracker, and keep personal applications out of GitHub.</x:v>
       </x:c>
       <x:c r="B206" s="42" t="str"/>
       <x:c r="C206" s="42" t="str"/>
@@ -2344,7 +2344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R452855507e1846fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f0d8d81b4814b45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4813,7 +4813,7 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="42" t="str">
-        <x:v>Review rows before relying on them. Salary, work type, and location can vary by website.</x:v>
+        <x:v>Check every row before relying on it, especially salary, work type, and location.</x:v>
       </x:c>
       <x:c r="B205" s="42" t="str"/>
       <x:c r="C205" s="42" t="str"/>
@@ -4827,7 +4827,7 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="42" t="str">
-        <x:v>The Job link column should keep the original posting URL.</x:v>
+        <x:v>Job link keeps the original posting URL.</x:v>
       </x:c>
       <x:c r="B206" s="42" t="str"/>
       <x:c r="C206" s="42" t="str"/>
@@ -4860,7 +4860,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf56e210a879e4afc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R757bc1022e7a4081"/>
   </x:tableParts>
 </x:worksheet>
 </file>